--- a/data/trans_orig/IP31KM01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM01_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>113249</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>106309</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>118038</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>108267</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>103274</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>111152</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>121698</t>
+          <t>112352</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101290</t>
+          <t>107292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129679</t>
+          <t>115295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>229966</t>
+          <t>225601</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211452</t>
+          <t>217581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238785</t>
+          <t>231353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9647</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16587</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3099</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10977</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>215026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>207417</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>221430</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>176157</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>169359</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>180566</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>230670</t>
+          <t>171225</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222029</t>
+          <t>165055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236794</t>
+          <t>175240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>406827</t>
+          <t>386249</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>396153</t>
+          <t>375567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415639</t>
+          <t>393775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9811</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23824</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9957</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16755</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142520</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132140</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149733</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>166861</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>157542</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>175404</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146395</t>
+          <t>125296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165122</t>
+          <t>139797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>324258</t>
+          <t>275986</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310419</t>
+          <t>263156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>336231</t>
+          <t>286800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16789</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34382</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21388</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12845</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30707</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>47081</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>146770</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>138085</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>153978</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>144563</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>135934</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>150854</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>157560</t>
+          <t>143730</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>136045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164655</t>
+          <t>150160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302123</t>
+          <t>290500</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290558</t>
+          <t>279108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310954</t>
+          <t>299444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19395</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12187</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28080</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19956</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13665</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28585</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51270</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>617565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601064</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>631556</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>831</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>595849</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>580984</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>606819</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>646433</t>
+          <t>547624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682126</t>
+          <t>572223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1238024</t>
+          <t>1159390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1281985</t>
+          <t>1197619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55268</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>85760</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>57285</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46315</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72150</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>126695</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>107412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159843</t>
+          <t>145641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
